--- a/data/nrm-github-data-fields.xlsx
+++ b/data/nrm-github-data-fields.xlsx
@@ -500,7 +500,7 @@
         <v>선택</v>
       </c>
       <c r="D9" t="str">
-        <v>비어 있으면 SerialNo가 설정된 모든 APK 사용자에게 표시. 값이 있으면 해당 SerialNo APK만 표시. APK SerialNo가 비어 있으면 알림 수집 안 함. "Admin"은 관리자 APK(SerialNo=Admin) 전용</v>
+        <v>비어 있으면 로그인한 모든 사용자에게 표시. 값이 있으면 해당 serial_no 계정만 표시. 로그인 serial이 없으면 알림을 수집하지 않음. 문의 등록 알림은 is_admin=y 계정마다 행을 하나씩 넣는다</v>
       </c>
     </row>
     <row r="10">
